--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J108-EnsembleFonction-RASS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J108-EnsembleFonction-RASS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="261">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251016120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-16T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -497,12 +497,6 @@
     <t>Préparateur en pharmacie (officine)</t>
   </si>
   <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>Auxiliaire de vie sociale</t>
-  </si>
-  <si>
     <t>319</t>
   </si>
   <si>
@@ -525,12 +519,6 @@
   </si>
   <si>
     <t>Assistant familial</t>
-  </si>
-  <si>
-    <t>323</t>
-  </si>
-  <si>
-    <t>Aide médico-psychologique (AMP)</t>
   </si>
   <si>
     <t>324</t>
@@ -1515,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2076,34 +2064,18 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>260</v>
+        <v>114</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>261</v>
+        <v>114</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>262</v>
+        <v>115</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
